--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H4"/>
+  <dimension ref="A4:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -466,6 +466,62 @@
           <t>Характеристика ответов обучающегося</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -675,7 +731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,7 +760,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -719,7 +774,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
@@ -734,7 +788,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
@@ -749,8 +802,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
@@ -765,7 +816,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
@@ -780,15 +830,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H6"/>
+  <dimension ref="A4:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -466,62 +466,6 @@
           <t>Характеристика ответов обучающегося</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -675,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,87 +693,107 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H4"/>
+  <dimension ref="A4:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -464,6 +464,48 @@
       <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Характеристика ответов обучающегося</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Маченко Юрий Юрьевич</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ыфввывфывфывфвыфвфыв</t>
         </is>
       </c>
     </row>
@@ -675,7 +717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,14 +735,14 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -721,79 +763,165 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Направление подготовки</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Дата экзамена</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Состав ГЭК утвержден приказом от</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Дата утверждения билетов</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Направление подготовки</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Дата защиты</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Состав ГЭК утвержден приказом от</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Допущен до защиты приказом от</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H5"/>
+  <dimension ref="A4:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -464,48 +464,6 @@
       <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Характеристика ответов обучающегося</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Маченко Юрий Юрьевич</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>ыфввывфывфывфвыфвфыв</t>
         </is>
       </c>
     </row>
@@ -717,7 +675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -729,196 +687,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ГЭК ТИУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Группа</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Дата экзамена</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Состав ГЭК утвержден приказом от</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Дата утверждения билетов</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Дата защиты</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Состав ГЭК утвержден приказом от</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Допущен до защиты приказом от</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Квалификация</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:H4"/>
+  <dimension ref="A4:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -464,6 +464,11 @@
       <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Характеристика ответов обучающегося</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
         </is>
       </c>
     </row>
@@ -478,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:L4"/>
+  <dimension ref="A4:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -540,6 +545,11 @@
       <c r="L4" s="1" t="inlineStr">
         <is>
           <t>Оценка</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>created_at</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U4"/>
+  <dimension ref="A4:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -661,6 +671,57 @@
       <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Отметить, что</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ыв</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ы</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>обучающийся готов к решению профессиональных задач, недостатков в теоретической и практической подготовке обучающегося не выявлено</t>
         </is>
       </c>
     </row>
@@ -675,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -690,6 +751,90 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>в</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U5"/>
+  <dimension ref="A4:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -671,57 +671,6 @@
       <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Отметить, что</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ыв</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>ы</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>обучающийся готов к решению профессиональных задач, недостатков в теоретической и практической подготовке обучающегося не выявлено</t>
         </is>
       </c>
     </row>
@@ -736,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,90 +697,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ГЭК ТИУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>в</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:I4"/>
+  <dimension ref="A4:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -469,6 +469,43 @@
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>вы</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Прикладная математика и информатика</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ПКТБ-22-1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>76 баллов (хорошо)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>В качестве результатов ГЭ были зачтены результаты полученные обучающимся при прохождении тестирования федерального интернет-экзамена для выпускника бакалавриата</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-04-19T01:02:41.265223</t>
         </is>
       </c>
     </row>
@@ -564,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U4"/>
+  <dimension ref="A4:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -671,6 +708,63 @@
       <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Отметить, что</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ФИО</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Прикладная математика и информатика</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ТЕМА</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>РУКОВОДИТЕЛЬ</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>61 (удовлетворительно)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>аспирант</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>обучающийся готов к решению профессиональных задач, недостатков в теоретической и практической подготовке обучающегося не выявлено</t>
         </is>
       </c>
     </row>
@@ -685,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +794,138 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Насиров Э.Б.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>а</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Направление подготовки</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Прикладная математика и информатика</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Группа</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ПКТБ-22-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Направление подготовки</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Прикладная математика и информатика</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>аспирант</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -475,7 +475,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>вы</t>
+          <t>Овсянников Игорь Сергеевич</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -485,17 +485,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Прикладная математика и информатика</t>
+          <t>38.03.05 Бизнес-информатика</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ПКТБ-22-1</t>
+          <t>ИСПб-21-1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>18 июня 2025 г</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>29 ноября 2024 г. № 955</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>76 баллов (хорошо)</t>
+          <t>91 баллов (отлично)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -505,7 +515,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-04-19T01:02:41.265223</t>
+          <t>2026-04-27T00:21:02.781759</t>
         </is>
       </c>
     </row>
@@ -601,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U5"/>
+  <dimension ref="A4:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -708,63 +718,6 @@
       <c r="U4" s="1" t="inlineStr">
         <is>
           <t>Отметить, что</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ФИО</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Прикладная математика и информатика</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ТЕМА</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>РУКОВОДИТЕЛЬ</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>61 (удовлетворительно)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>аспирант</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>обучающийся готов к решению профессиональных задач, недостатков в теоретической и практической подготовке обучающегося не выявлено</t>
         </is>
       </c>
     </row>
@@ -779,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -797,84 +750,70 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Насиров Э.Б.</t>
+          <t xml:space="preserve">Тарасенко А.В. </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>генеральный директор ООО ЭХО</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>Григорьев А.М.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>заместитель директора МКУ  Комитет по информатизации города Тюмени</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>Барбаков О.М.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>профессор, д.с.н., заведующий кафедры МИПИТ ТИУ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>Аханова М.А.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>а</t>
+          <t>доцент, к.с.н. кафедры МИПИТ ТИУ</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>а</t>
+          <t xml:space="preserve">Локотаева И.Г. </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>а</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>а</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>а</t>
+          <t xml:space="preserve">старший преподаватель </t>
         </is>
       </c>
     </row>
@@ -886,7 +825,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Прикладная математика и информатика</t>
+          <t>38.03.05 Бизнес-информатика</t>
         </is>
       </c>
     </row>
@@ -898,31 +837,31 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Прикладная математика и информатика</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Квалификация</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>аспирант</t>
+          <t>ИСПб-21-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Дата экзамена</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>18 июня 2025 г</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Состав ГЭК утвержден приказом от</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>29 ноября 2024 г. № 955</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:I5"/>
+  <dimension ref="A4:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -469,53 +469,6 @@
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Овсянников Игорь Сергеевич</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>38.03.05 Бизнес-информатика</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ИСПб-21-1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>18 июня 2025 г</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>29 ноября 2024 г. № 955</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>91 баллов (отлично)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>В качестве результатов ГЭ были зачтены результаты полученные обучающимся при прохождении тестирования федерального интернет-экзамена для выпускника бакалавриата</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-04-27T00:21:02.781759</t>
         </is>
       </c>
     </row>
@@ -732,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +770,20 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>121212</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12121212</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -862,6 +829,78 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>29 ноября 2024 г. № 955</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Дата утверждения билетов</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ААААААААААААААААААААА</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Направление подготовки</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ывфвdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Дата защиты</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>авd</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Состав ГЭК утвержден приказом от</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>выа</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Допущен до защиты приказом от</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ыав</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>бакалавр</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -703,7 +703,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Тарасенко А.В. </t>
+          <t>Тарасенко А.В.</t>
         </is>
       </c>
     </row>
@@ -714,6 +714,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -728,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
@@ -742,6 +744,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
@@ -756,6 +759,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
@@ -770,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -714,7 +714,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -729,7 +728,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
@@ -744,7 +742,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
@@ -759,8 +756,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
@@ -775,7 +770,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:I4"/>
+  <dimension ref="A4:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -469,6 +469,48 @@
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Дубровина Екатерина Васильевна</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>91 баллов (отлично)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-05-11T00:16:38.665387</t>
         </is>
       </c>
     </row>
@@ -483,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:M4"/>
+  <dimension ref="A4:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -550,6 +592,53 @@
       <c r="M4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Смолик Ангелина Дмитриевна</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>61 баллов (удовлетворительно)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2026-05-11T00:18:42.615350</t>
         </is>
       </c>
     </row>
@@ -564,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:U4"/>
+  <dimension ref="A4:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -668,9 +757,66 @@
           <t>Выдать диплом</t>
         </is>
       </c>
-      <c r="U4" s="1" t="inlineStr">
-        <is>
-          <t>Отметить, что</t>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Кузьмин Дмитрий Владимирович</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Автоматизация и оптимизация бизнес-процессов проектной деятельности кафедры ТИУ.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>76 (хорошо)</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>аспирант</t>
         </is>
       </c>
     </row>
@@ -703,132 +849,132 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Тарасенко А.В.</t>
+          <t>10!</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>генеральный директор ООО ЭХО</t>
+          <t>20!</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Григорьев А.М.</t>
+          <t>30!</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>заместитель директора МКУ  Комитет по информатизации города Тюмени</t>
+          <t>40!</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Барбаков О.М.</t>
+          <t>50!</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>профессор, д.с.н., заведующий кафедры МИПИТ ТИУ</t>
+          <t>60!</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Аханова М.А.</t>
+          <t>70!</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>доцент, к.с.н. кафедры МИПИТ ТИУ</t>
+          <t>80!</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Локотаева И.Г. </t>
+          <t>110!</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">старший преподаватель </t>
+          <t>120!</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>121212</t>
+          <t>90!</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>12121212</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>38.03.05 Бизнес-информатика</t>
+          <t>100!</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Группа</t>
+          <t>Направление подготовки</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ИСПб-21-1</t>
+          <t>130!</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Дата экзамена</t>
+          <t>Группа</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18 июня 2025 г</t>
+          <t>140!</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Дата экзамена</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>150!</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Состав ГЭК утвержден приказом от</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>29 ноября 2024 г. № 955</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>160!</t>
         </is>
       </c>
     </row>
@@ -840,7 +986,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ААААААААААААААААААААА</t>
+          <t>170!</t>
         </is>
       </c>
     </row>
@@ -852,7 +998,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ывфвdd</t>
+          <t>180!</t>
         </is>
       </c>
     </row>
@@ -864,7 +1010,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>авd</t>
+          <t>190!</t>
         </is>
       </c>
     </row>
@@ -876,7 +1022,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>выа</t>
+          <t>200!</t>
         </is>
       </c>
     </row>
@@ -888,7 +1034,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ыав</t>
+          <t>210!</t>
         </is>
       </c>
     </row>
@@ -900,7 +1046,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>бакалавр</t>
+          <t>аспирант000!</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:I5"/>
+  <dimension ref="A4:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -475,7 +475,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Дубровина Екатерина Васильевна</t>
+          <t>Бронников Гордей Константинович</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -483,34 +483,68 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>16</t>
+          <t>ПКТБ-22-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>91 баллов (отлично)</t>
+          <t>76 баллов (хорошо)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-11T00:16:38.665387</t>
+          <t>2026-05-14T21:11:21.000127</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Понамарёв Павел Андреевич</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ПКТБ-22-1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>76 баллов (хорошо)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-05-15T16:14:36.906345</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Гемель Алиса Ильинична</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ПКТБ-22-1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>61 баллов (удовлетворительно)</t>
         </is>
       </c>
     </row>
@@ -525,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:M5"/>
+  <dimension ref="A4:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -598,47 +632,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Смолик Ангелина Дмитриевна</t>
+          <t>Кузьмин Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>17</t>
+          <t>ПКТБ-22-1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>61 баллов (удовлетворительно)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-05-11T00:18:42.615350</t>
+          <t>91 баллов (отлично)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Стенькин Артур Васильевич</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ПКТБ-22-1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>76 баллов (хорошо)</t>
         </is>
       </c>
     </row>
@@ -653,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:T5"/>
+  <dimension ref="A4:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -761,7 +792,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Кузьмин Дмитрий Владимирович</t>
+          <t>Бронников Гордей Константинович</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -769,24 +800,19 @@
           <t>1-1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Автоматизация и оптимизация бизнес-процессов проектной деятельности кафедры ТИУ.</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Автоматизация и оптимизация бизнес-процессов образовательной деятельности кафедры ВУЗа (на примере кафедры МиПИТ ТИУ)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Спирин И.С.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ч</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -794,11 +820,6 @@
           <t>–</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>–</t>
@@ -811,12 +832,49 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>91 (отлично)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Дежурко Антон Владимирович</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Автоматизация и оптимизация бизнес-процессов по подбору персонала.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Барбаков О.М.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>76 (хорошо)</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>аспирант</t>
         </is>
       </c>
     </row>
@@ -831,7 +889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -849,84 +907,90 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>10!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>20!</t>
-        </is>
-      </c>
-    </row>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>30!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>40!</t>
-        </is>
-      </c>
-    </row>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>50!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>60!</t>
-        </is>
-      </c>
-    </row>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>70!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>80!</t>
-        </is>
-      </c>
-    </row>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>110!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>120!</t>
-        </is>
-      </c>
-    </row>
+          <t>А</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>90!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>100!</t>
+          <t>А</t>
         </is>
       </c>
     </row>
@@ -938,7 +1002,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>130!</t>
+          <t>в</t>
         </is>
       </c>
     </row>
@@ -950,7 +1014,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>140!</t>
+          <t>ПКТБ-22-1</t>
         </is>
       </c>
     </row>
@@ -962,7 +1026,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>150!</t>
+          <t>ыв</t>
         </is>
       </c>
     </row>
@@ -974,7 +1038,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>160!</t>
+          <t>ыв</t>
         </is>
       </c>
     </row>
@@ -986,67 +1050,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>170!</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>180!</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Дата защиты</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>190!</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Состав ГЭК утвержден приказом от</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>200!</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Допущен до защиты приказом от</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>210!</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Квалификация</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>аспирант000!</t>
+          <t>ыв</t>
         </is>
       </c>
     </row>

--- a/data/БД.xlsx
+++ b/data/БД.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:I7"/>
+  <dimension ref="A4:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -469,82 +469,6 @@
       <c r="I4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Бронников Гордей Константинович</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>76 баллов (хорошо)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-05-14T21:11:21.000127</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Понамарёв Павел Андреевич</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>76 баллов (хорошо)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-05-15T16:14:36.906345</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Гемель Алиса Ильинична</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>61 баллов (удовлетворительно)</t>
         </is>
       </c>
     </row>
@@ -559,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:M6"/>
+  <dimension ref="A4:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -626,50 +550,6 @@
       <c r="M4" s="1" t="inlineStr">
         <is>
           <t>created_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Кузьмин Дмитрий Владимирович</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>91 баллов (отлично)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Стенькин Артур Васильевич</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>76 баллов (хорошо)</t>
         </is>
       </c>
     </row>
@@ -684,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:T6"/>
+  <dimension ref="A4:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -786,95 +666,6 @@
       <c r="T4" s="1" t="inlineStr">
         <is>
           <t>Выдать диплом</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Бронников Гордей Константинович</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Автоматизация и оптимизация бизнес-процессов образовательной деятельности кафедры ВУЗа (на примере кафедры МиПИТ ТИУ)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Спирин И.С.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Ч</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>91 (отлично)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Дежурко Антон Владимирович</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Автоматизация и оптимизация бизнес-процессов по подбору персонала.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Барбаков О.М.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>76 (хорошо)</t>
         </is>
       </c>
     </row>
@@ -889,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,156 +692,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ГЭК ТИУ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16">
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>А</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Направление подготовки</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>в</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Группа</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ПКТБ-22-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Дата экзамена</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ыв</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Состав ГЭК утвержден приказом от</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ыв</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Дата утверждения билетов</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ыв</t>
         </is>
       </c>
     </row>
